--- a/Datos/Casos resueltos.xlsx
+++ b/Datos/Casos resueltos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,45 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>Tiene un tatuaje de una frase inspiradora en el cuello</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Diego Cáceres</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelo rubio ondulado, ojos verdes, tez morena</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NEA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Tiene un tatuaje de una frase inspiradora en la espalda</t>
         </is>
       </c>
     </row>

--- a/Datos/Casos resueltos.xlsx
+++ b/Datos/Casos resueltos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,123 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Florencia Romero</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelo castaño oscuro rizado, ojos verdes, tez clara</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cuyo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tiene un tatuaje de un león en el hombro</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paula Benítez</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelo pelirrojo rizado, ojos celestes, tez morena</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>GBA Sur</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tiene un tatuaje de un fénix en el brazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalo Silva</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelo rapado, ojos celestes, tez clara</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>GBA Oeste</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Usa ropa oversize en tonos oscuros</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datos/Casos resueltos.xlsx
+++ b/Datos/Casos resueltos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,313 +477,79 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matías López</t>
+          <t>Martina Díaz</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.90000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelo castaño oscuro rizado, ojos celestes, tez clara</t>
+          <t>Pelo rapado, ojos oscuros, tez pálida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>GBA Norte</t>
+          <t>GBA Oeste</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tiene un tatuaje de un fénix en el cuello</t>
+          <t>Tiene un tatuaje de figuras geométricas en el brazo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Florencia Romero</t>
+          <t>Matías López</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelo castaño oscuro rizado, ojos verdes, tez clara</t>
+          <t>Pelo castaño oscuro rizado, ojos celestes, tez clara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cuyo</t>
+          <t>GBA Norte</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tiene un tatuaje de un león en el hombro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gonzalo Silva</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pelo rapado, ojos celestes, tez clara</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>GBA Oeste</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Usa ropa oversize en tonos oscuros</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Florencia Flores</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>63</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pelo negro corto, ojos verdes, tez pálida</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Cuyo</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Tiene un tatuaje de una frase inspiradora en el cuello</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Diego Cáceres</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pelo rubio ondulado, ojos verdes, tez morena</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>NEA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Tiene un tatuaje de una frase inspiradora en la espalda</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Florencia Romero</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pelo castaño oscuro rizado, ojos verdes, tez clara</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Cuyo</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Tiene un tatuaje de un león en el hombro</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Paula Benítez</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>55</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pelo pelirrojo rizado, ojos celestes, tez morena</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>GBA Sur</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tiene un tatuaje de un fénix en el brazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Gonzalo Silva</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>32</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pelo rapado, ojos celestes, tez clara</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>GBA Oeste</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Usa ropa oversize en tonos oscuros</t>
+          <t>Tiene un tatuaje de un fénix en el cuello</t>
         </is>
       </c>
     </row>

--- a/Datos/Casos resueltos.xlsx
+++ b/Datos/Casos resueltos.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>N° Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nombre y Apellido</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Edad</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Género</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Peso (kg)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Altura (m)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Rasgos Físicos</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Zona (Argentina)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Datos Extra</t>
         </is>
@@ -550,6 +538,45 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Tiene un tatuaje de un fénix en el cuello</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Martín Ramírez</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>52</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pelo castaño lacio, ojos miel, tez clara</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tiene un tatuaje de una constelación en la pierna</t>
         </is>
       </c>
     </row>
